--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.30965070197148</v>
+        <v>2.812818239070366</v>
       </c>
       <c r="D2" t="n">
-        <v>23.05950708878832</v>
+        <v>3.747169901928102</v>
       </c>
       <c r="E2" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F2" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.557171171575092</v>
+        <v>0.5780403153809525</v>
       </c>
       <c r="D3" t="n">
-        <v>10.30368721817538</v>
+        <v>1.674349172953499</v>
       </c>
       <c r="E3" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F3" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.72286426827445</v>
+        <v>2.554965443594599</v>
       </c>
       <c r="D4" t="n">
-        <v>8.790172041714582</v>
+        <v>1.42840295677862</v>
       </c>
       <c r="E4" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F4" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.85978573194554</v>
+        <v>4.852215181441149</v>
       </c>
       <c r="D5" t="n">
-        <v>20.12952264673971</v>
+        <v>3.271047430095202</v>
       </c>
       <c r="E5" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F5" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.69739869321752</v>
+        <v>6.125827287647846</v>
       </c>
       <c r="D6" t="n">
-        <v>23.74412209882408</v>
+        <v>3.858419841058913</v>
       </c>
       <c r="E6" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F6" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.46605578737058</v>
+        <v>5.92573406544772</v>
       </c>
       <c r="D7" t="n">
-        <v>39.01163845832046</v>
+        <v>6.339391249477075</v>
       </c>
       <c r="E7" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F7" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.87199254874426</v>
+        <v>6.804198789170942</v>
       </c>
       <c r="D8" t="n">
-        <v>34.82701976823942</v>
+        <v>5.659390712338906</v>
       </c>
       <c r="E8" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F8" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.77587031918408</v>
+        <v>4.838578926867412</v>
       </c>
       <c r="D9" t="n">
-        <v>35.30621085105161</v>
+        <v>5.737259263295887</v>
       </c>
       <c r="E9" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F9" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.60328984366986</v>
+        <v>8.223034599596353</v>
       </c>
       <c r="D10" t="n">
-        <v>63.31452582076494</v>
+        <v>10.2886104458743</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F10" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>49.04903034503787</v>
+        <v>7.970467431068654</v>
       </c>
       <c r="D11" t="n">
-        <v>34.20759070765099</v>
+        <v>5.558733489993285</v>
       </c>
       <c r="E11" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F11" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.27375033875835</v>
+        <v>7.844484430048233</v>
       </c>
       <c r="D12" t="n">
-        <v>28.6356421265527</v>
+        <v>4.653291845564813</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F12" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.38462486592471</v>
+        <v>5.100001540712766</v>
       </c>
       <c r="D13" t="n">
-        <v>21.33051040012989</v>
+        <v>3.466207940021107</v>
       </c>
       <c r="E13" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F13" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.5060581176929</v>
+        <v>2.519734444125097</v>
       </c>
       <c r="D14" t="n">
-        <v>14.69751291664052</v>
+        <v>2.388345848954085</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F14" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.85428281505659</v>
+        <v>3.876320957446696</v>
       </c>
       <c r="D15" t="n">
-        <v>23.98953914307275</v>
+        <v>3.898300110749322</v>
       </c>
       <c r="E15" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F15" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.50815315716656</v>
+        <v>4.795074888039567</v>
       </c>
       <c r="D16" t="n">
-        <v>29.55248097713742</v>
+        <v>4.802278158784831</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3421808129258</v>
+        <v>2.168104382100442</v>
       </c>
       <c r="F16" t="n">
-        <v>12.98294421423586</v>
+        <v>2.109728434813328</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
